--- a/output/pdf_financials_xlsx/CEO.H.xlsx
+++ b/output/pdf_financials_xlsx/CEO.H.xlsx
@@ -6058,43 +6058,43 @@
         <v>0.721483</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.721483</v>
       </c>
     </row>
     <row r="93">
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0.025</v>
@@ -9556,7 +9556,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -10716,7 +10720,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11318,7 +11326,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -21812,7 +21824,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CEO.H.xlsx
+++ b/output/pdf_financials_xlsx/CEO.H.xlsx
@@ -939,49 +939,49 @@
         <v>0.031016</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.08733</v>
+        <v>0.118102</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.527423</v>
+        <v>0.724948</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.083958</v>
+        <v>0.153098</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.06404</v>
+        <v>0.101814</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.076075</v>
+        <v>0.120468</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.06737799999999999</v>
+        <v>0.120141</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.024649</v>
+        <v>0.059946</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.010464</v>
+        <v>0.0471</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.011703</v>
+        <v>0.04743</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.032295</v>
+        <v>0.052452</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.037753</v>
+        <v>0.051028</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.038734</v>
+        <v>0.055534</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.038939</v>
+        <v>0.055439</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.035233</v>
+        <v>0.052133</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.035241</v>
+        <v>0.052841</v>
       </c>
     </row>
     <row r="11">
@@ -1022,34 +1022,34 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.06737799999999999</v>
+        <v>-0.120141</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.024649</v>
+        <v>-0.059946</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.010464</v>
+        <v>-0.0471</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.011703</v>
+        <v>-0.04743</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.032295</v>
+        <v>-0.052452</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.037753</v>
+        <v>-0.051028</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.038734</v>
+        <v>-0.055534</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.038939</v>
+        <v>-0.055439</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.035233</v>
+        <v>-0.052133</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.035241</v>
+        <v>-0.052841</v>
       </c>
     </row>
     <row r="12">
@@ -1074,40 +1074,40 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007706</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.007974999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.016695</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.036074</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.0117</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.011935</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.011732</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.0117</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.0117</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.011704</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.011732</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="13">
@@ -2096,40 +2096,40 @@
         <v>-0.148098</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.094108</v>
+        <v>-0.101814</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.064156</v>
+        <v>-0.072131</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.103567</v>
+        <v>-0.120262</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.276091</v>
+        <v>-0.312165</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.0354</v>
+        <v>-0.0471</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.036293</v>
+        <v>-0.048228</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.041518</v>
+        <v>-0.05325</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.038729</v>
+        <v>-0.050429</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.043434</v>
+        <v>-0.055134</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.045252</v>
+        <v>-0.056956</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.040425</v>
+        <v>-0.052157</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.040926</v>
+        <v>-0.052626</v>
       </c>
     </row>
     <row r="28">
@@ -2212,40 +2212,40 @@
         <v>-0.148098</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.094108</v>
+        <v>-0.101814</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.064156</v>
+        <v>-0.072131</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.103567</v>
+        <v>-0.120262</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.276091</v>
+        <v>-0.312165</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.0354</v>
+        <v>-0.0471</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.036293</v>
+        <v>-0.048228</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.041518</v>
+        <v>-0.05325</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.038729</v>
+        <v>-0.050429</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.043434</v>
+        <v>-0.055134</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.045252</v>
+        <v>-0.056956</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.040425</v>
+        <v>-0.052157</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.040926</v>
+        <v>-0.052626</v>
       </c>
     </row>
     <row r="30">
@@ -2504,16 +2504,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.055779</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.477529</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.936044</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.937723</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.823038</v>
@@ -2528,31 +2528,31 @@
         <v>0.09712899999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.06378499999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.066333</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.066843</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.01943</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.014902</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.008666999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.010738</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.010665</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.010593</v>
       </c>
     </row>
     <row r="35">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.055779</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.477529</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.936044</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.937723</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.823038</v>
@@ -2644,31 +2644,31 @@
         <v>0.099219</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.001596</v>
+        <v>0.06538099999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.002394</v>
+        <v>0.068727</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.001596</v>
+        <v>0.068439</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.000798</v>
+        <v>0.020228</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.001397</v>
+        <v>0.016299</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.001796</v>
+        <v>0.010463</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.000279</v>
+        <v>0.011017</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.000255</v>
+        <v>0.01092</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.000471</v>
+        <v>0.011064</v>
       </c>
     </row>
     <row r="37">
@@ -3319,13 +3319,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.477529</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.936044</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.9389729999999999</v>
+        <v>0.00125</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26663,7 +26663,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -33182,7 +33182,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">

--- a/output/pdf_financials_xlsx/CEO.H.xlsx
+++ b/output/pdf_financials_xlsx/CEO.H.xlsx
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.041959</v>
+        <v>0.071959</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.031016</v>
+        <v>0.061016</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.08344699999999999</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.041959</v>
+        <v>0.071959</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.031016</v>
+        <v>0.061016</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.118102</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.041959</v>
+        <v>-0.071959</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.031016</v>
+        <v>-0.061016</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.000278</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.000222</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>2.624092</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>3.098092</v>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.088129</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.114129</v>
@@ -15346,7 +15346,11 @@
           <t>Equipment – Notes 4 and 5</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>0.000278</v>
       </c>
@@ -15647,7 +15651,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>2.624092</v>
       </c>
@@ -15746,7 +15754,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>0.088129</v>
       </c>
@@ -34917,7 +34929,11 @@
           <t>Management fees – Note 5</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E266" s="5" t="n">
         <v>0.03</v>
       </c>
@@ -35115,7 +35131,11 @@
           <t>Professional fees – Note 5</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E268" s="5" t="n">
         <v>0.049181</v>
       </c>

--- a/output/pdf_financials_xlsx/CEO.H.xlsx
+++ b/output/pdf_financials_xlsx/CEO.H.xlsx
@@ -567,8 +567,10 @@
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -693,8 +695,10 @@
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
@@ -759,10 +763,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.071959</v>
+        <v>0.079733</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.061016</v>
+        <v>0.06944</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.08344699999999999</v>
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.071959</v>
+        <v>0.079733</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.061016</v>
+        <v>0.06944</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.118102</v>
@@ -991,10 +995,12 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.071959</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>-0.061016</v>
+        <v>-0.079733</v>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -4336,16 +4342,16 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.126418</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.057267</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.000887</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.00176</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4507,19 +4513,19 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.007875</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.014378</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -6522,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002945</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.007833</v>
@@ -6812,7 +6818,7 @@
         <v>0.00304</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.022058</v>
+        <v>0.019113</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.019533</v>
@@ -7102,7 +7108,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.025645</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7288,13 +7294,13 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.020246</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.073604</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.00209</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -7349,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.091405</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.020125</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -8510,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.025645</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8568,7 +8574,7 @@
         <v>-0.130326</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.08906799999999999</v>
+        <v>-0.114713</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.091485</v>
@@ -8629,7 +8635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U275"/>
+  <dimension ref="A1:U290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16073,10 +16079,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="5" t="n">
+        <v>-0.116523</v>
       </c>
       <c r="G76" s="5" t="n">
         <v>-0.118102</v>
@@ -16241,10 +16245,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" s="5" t="n">
+        <v>-0.002945</v>
       </c>
       <c r="G78" s="5" t="n">
         <v>-0.007833</v>
@@ -16318,10 +16320,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F79" s="5" t="n">
+        <v>0.022058</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>0.027366</v>
@@ -17218,10 +17218,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="5" t="n">
+        <v>0.036463</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>0.00704</v>
@@ -18000,7 +17998,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -18097,7 +18099,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -20630,10 +20636,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="5" t="n">
+        <v>0.00389</v>
       </c>
       <c r="G123" s="5" t="n">
         <v>4.4e-05</v>
@@ -21947,10 +21951,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F136" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="G136" s="5" t="n">
         <v>0.55</v>
@@ -22359,10 +22361,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F140" s="5" t="n">
+        <v>0.477529</v>
       </c>
       <c r="G140" s="5" t="n">
         <v>0.936044</v>
@@ -22460,10 +22460,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F141" s="5" t="n">
+        <v>0.42175</v>
       </c>
       <c r="G141" s="5" t="n">
         <v>0.458515</v>
@@ -22563,10 +22561,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F142" s="5" t="n">
+        <v>0.055779</v>
       </c>
       <c r="G142" s="5" t="n">
         <v>0.477529</v>
@@ -22648,24 +22644,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="n">
-        <v>-0.128982</v>
+          <t>Loan receivable</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>-0.116523</v>
+        <v>0.004452</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -22751,29 +22745,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>6.8e-05</v>
+          <t>Changes in non-cash operating working capital total</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.00389</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.052605</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>-0.091485</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -22854,22 +22844,26 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GST recoverable</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Purchase of property and equipment</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>-0.002945</v>
+        <v>-0.025645</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -22955,20 +22949,26 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Loan receivable</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="n">
-        <v>-0.004452</v>
+          <t>Investing activities total</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.004452</v>
+        <v>-0.025645</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -23054,24 +23054,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="n">
-        <v>0.00304</v>
+          <t>Shares and share purchase warrants issued as finder’s fees</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0.022058</v>
+        <v>0.076</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -23157,24 +23155,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>-0.130326</v>
+          <t>Sale of assets to settle related party debt</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-0.08906799999999999</v>
+        <v>0.021811</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -23260,12 +23256,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Investing Activity</t>
+          <t>Supplemental disclosures</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Purchase of vehicle</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -23274,8 +23270,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F149" s="5" t="n">
-        <v>-0.025645</v>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -23361,26 +23359,24 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Investing Activity</t>
+          <t>Supplemental disclosures</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F150" s="5" t="n">
-        <v>-0.025645</v>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -23466,22 +23462,24 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Due to directors</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>-0.128982</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.036463</v>
+        <v>-0.116523</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -23567,22 +23565,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Increase in share capital</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>6.8e-05</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>0.5</v>
+        <v>0.00389</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -23668,22 +23668,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Share subscriptions received</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" s="5" t="n">
-        <v>0.08437500000000001</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GST recoverable</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>-0.002945</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -23769,24 +23773,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Loan receivable</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" s="5" t="n">
-        <v>0.08437500000000001</v>
+        <v>-0.004452</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.536463</v>
+        <v>0.004452</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -23872,20 +23872,24 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash during the year</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E155" s="5" t="n">
-        <v>-0.045951</v>
+        <v>0.00304</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>0.42175</v>
+        <v>0.022058</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -23971,24 +23975,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.10173</v>
+        <v>-0.130326</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.055779</v>
+        <v>-0.08906799999999999</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -24074,24 +24078,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="n">
-        <v>0.055779</v>
+          <t>Purchase of vehicle</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0.477529</v>
+        <v>-0.025645</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -24177,24 +24179,26 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Cash paid for</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Interest $</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F158" s="5" t="n">
+        <v>-0.025645</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -24280,12 +24284,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cash paid for</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Income taxes $</t>
+          <t>Due to directors</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -24294,10 +24298,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F159" s="5" t="n">
+        <v>0.036463</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -24378,33 +24380,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Increase in share capital</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F160" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -24416,11 +24412,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="5" t="n">
-        <v>0.032059</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>0.032101</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -24467,52 +24467,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T160" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U160" s="5" t="n">
-        <v>0.03</v>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share subscriptions received</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" s="5" t="n">
+        <v>0.08437500000000001</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G161" s="5" t="n">
-        <v>0.015186</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>0.023828</v>
-      </c>
-      <c r="I161" s="5" t="n">
-        <v>0.039214</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -24534,61 +24538,73 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N161" s="5" t="n">
-        <v>0.010464</v>
-      </c>
-      <c r="O161" s="5" t="n">
-        <v>0.011703</v>
-      </c>
-      <c r="P161" s="5" t="n">
-        <v>0.009795</v>
-      </c>
-      <c r="Q161" s="5" t="n">
-        <v>0.007753</v>
-      </c>
-      <c r="R161" s="5" t="n">
-        <v>0.008734</v>
-      </c>
-      <c r="S161" s="5" t="n">
-        <v>0.008939000000000001</v>
-      </c>
-      <c r="T161" s="5" t="n">
-        <v>0.005233</v>
-      </c>
-      <c r="U161" s="5" t="n">
-        <v>0.005241</v>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>0.536463</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -24640,129 +24656,157 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q162" s="5" t="n">
-        <v>0.013275</v>
-      </c>
-      <c r="R162" s="5" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="S162" s="5" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="T162" s="5" t="n">
-        <v>0.0169</v>
-      </c>
-      <c r="U162" s="5" t="n">
-        <v>0.0176</v>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="n">
-        <v>0.118102</v>
-      </c>
-      <c r="H163" s="5" t="n">
-        <v>0.724948</v>
-      </c>
-      <c r="I163" s="5" t="n">
-        <v>0.153098</v>
-      </c>
-      <c r="J163" s="5" t="n">
-        <v>0.101814</v>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>0.120468</v>
-      </c>
-      <c r="L163" s="5" t="n">
-        <v>0.120141</v>
-      </c>
-      <c r="M163" s="5" t="n">
-        <v>0.059946</v>
-      </c>
-      <c r="N163" s="5" t="n">
-        <v>0.0471</v>
-      </c>
-      <c r="O163" s="5" t="n">
-        <v>0.04743</v>
-      </c>
-      <c r="P163" s="5" t="n">
-        <v>0.052452</v>
-      </c>
-      <c r="Q163" s="5" t="n">
-        <v>0.051028</v>
-      </c>
-      <c r="R163" s="5" t="n">
-        <v>0.055534</v>
-      </c>
-      <c r="S163" s="5" t="n">
-        <v>0.055439</v>
-      </c>
-      <c r="T163" s="5" t="n">
-        <v>0.052133</v>
-      </c>
-      <c r="U163" s="5" t="n">
-        <v>0.052841</v>
+          <t>Increase (decrease) in cash during the year</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" s="5" t="n">
+        <v>-0.045951</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Loss before other income (expense)</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>0.10173</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>0.055779</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -24779,73 +24823,93 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J164" s="5" t="n">
-        <v>-0.101814</v>
-      </c>
-      <c r="K164" s="5" t="n">
-        <v>-0.120468</v>
-      </c>
-      <c r="L164" s="5" t="n">
-        <v>-0.120141</v>
-      </c>
-      <c r="M164" s="5" t="n">
-        <v>-0.059946</v>
-      </c>
-      <c r="N164" s="5" t="n">
-        <v>-0.0471</v>
-      </c>
-      <c r="O164" s="5" t="n">
-        <v>-0.04743</v>
-      </c>
-      <c r="P164" s="5" t="n">
-        <v>-0.052452</v>
-      </c>
-      <c r="Q164" s="5" t="n">
-        <v>-0.051028</v>
-      </c>
-      <c r="R164" s="5" t="n">
-        <v>-0.055534</v>
-      </c>
-      <c r="S164" s="5" t="n">
-        <v>-0.055439</v>
-      </c>
-      <c r="T164" s="5" t="n">
-        <v>-0.052133</v>
-      </c>
-      <c r="U164" s="5" t="n">
-        <v>-0.052841</v>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Interest income (Note 4)</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>0.055779</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>0.477529</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -24887,42 +24951,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O165" s="5" t="n">
-        <v>0.011935</v>
-      </c>
-      <c r="P165" s="5" t="n">
-        <v>0.011732</v>
-      </c>
-      <c r="Q165" s="5" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="R165" s="5" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="S165" s="5" t="n">
-        <v>0.011704</v>
-      </c>
-      <c r="T165" s="5" t="n">
-        <v>0.011732</v>
-      </c>
-      <c r="U165" s="5" t="n">
-        <v>0.0117</v>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Cash paid for</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities</t>
+          <t>Interest $</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -24966,11 +25044,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M166" s="5" t="n">
-        <v>-0.000494</v>
-      </c>
-      <c r="N166" s="5" t="n">
-        <v>0.000798</v>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -24997,34 +25079,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T166" s="5" t="n">
-        <v>-2.4e-05</v>
-      </c>
-      <c r="U166" s="5" t="n">
-        <v>0.000215</v>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Cash paid for</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Total other income (expense)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Income taxes $</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -25050,41 +25132,65 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J167" s="5" t="n">
-        <v>0.007706</v>
-      </c>
-      <c r="K167" s="5" t="n">
-        <v>0.056312</v>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v>0.016574</v>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v>-0.216145</v>
-      </c>
-      <c r="N167" s="5" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="O167" s="5" t="n">
-        <v>0.011137</v>
-      </c>
-      <c r="P167" s="5" t="n">
-        <v>0.010934</v>
-      </c>
-      <c r="Q167" s="5" t="n">
-        <v>0.012299</v>
-      </c>
-      <c r="R167" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="S167" s="5" t="n">
-        <v>0.010187</v>
-      </c>
-      <c r="T167" s="5" t="n">
-        <v>0.011708</v>
-      </c>
-      <c r="U167" s="5" t="n">
-        <v>0.011915</v>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -25095,17 +25201,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Management fees (Note 8)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -25128,15 +25234,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I168" s="5" t="n">
+        <v>0.032059</v>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>0.032101</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -25163,23 +25265,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P168" s="5" t="n">
-        <v>-0.041518</v>
-      </c>
-      <c r="Q168" s="5" t="n">
-        <v>-0.038729</v>
-      </c>
-      <c r="R168" s="5" t="n">
-        <v>-0.043434</v>
-      </c>
-      <c r="S168" s="5" t="n">
-        <v>-0.045252</v>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T168" s="5" t="n">
-        <v>-0.040425</v>
+        <v>0.03</v>
       </c>
       <c r="U168" s="5" t="n">
-        <v>-0.040926</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="169">
@@ -25190,17 +25300,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -25208,25 +25318,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F169" s="5" t="n">
+        <v>0.008521000000000001</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.015186</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>0.023828</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>0.039214</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -25243,48 +25345,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M169" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="5" t="n">
+        <v>0.010464</v>
+      </c>
+      <c r="O169" s="5" t="n">
+        <v>0.011703</v>
+      </c>
+      <c r="P169" s="5" t="n">
+        <v>0.009795</v>
+      </c>
+      <c r="Q169" s="5" t="n">
+        <v>0.007753</v>
+      </c>
+      <c r="R169" s="5" t="n">
+        <v>0.008734</v>
+      </c>
+      <c r="S169" s="5" t="n">
+        <v>0.008939000000000001</v>
+      </c>
+      <c r="T169" s="5" t="n">
+        <v>0.005233</v>
+      </c>
+      <c r="U169" s="5" t="n">
+        <v>0.005241</v>
       </c>
     </row>
     <row r="170">
@@ -25295,17 +25383,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -25333,41 +25421,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J170" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="K170" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="L170" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="M170" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="N170" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="O170" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="P170" s="5" t="n">
-        <v>34.283475</v>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q170" s="5" t="n">
-        <v>34.283475</v>
+        <v>0.013275</v>
       </c>
       <c r="R170" s="5" t="n">
-        <v>34.283475</v>
+        <v>0.0168</v>
       </c>
       <c r="S170" s="5" t="n">
-        <v>34.283475</v>
+        <v>0.0165</v>
       </c>
       <c r="T170" s="5" t="n">
-        <v>34.283475</v>
+        <v>0.0169</v>
       </c>
       <c r="U170" s="5" t="n">
-        <v>34.283475</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="171">
@@ -25378,15 +25480,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2023 34,283,475 3,763,592 721,483</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -25397,76 +25503,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G171" s="5" t="n">
+        <v>0.118102</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>0.724948</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>0.153098</v>
+      </c>
+      <c r="J171" s="5" t="n">
+        <v>0.101814</v>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>0.120468</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>0.120141</v>
+      </c>
+      <c r="M171" s="5" t="n">
+        <v>0.059946</v>
+      </c>
+      <c r="N171" s="5" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="O171" s="5" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="P171" s="5" t="n">
+        <v>0.052452</v>
+      </c>
+      <c r="Q171" s="5" t="n">
+        <v>0.051028</v>
+      </c>
+      <c r="R171" s="5" t="n">
+        <v>0.055534</v>
+      </c>
+      <c r="S171" s="5" t="n">
+        <v>0.055439</v>
       </c>
       <c r="T171" s="5" t="n">
-        <v>-0.135294</v>
+        <v>0.052133</v>
       </c>
       <c r="U171" s="5" t="n">
-        <v>-4.620369</v>
+        <v>0.052841</v>
       </c>
     </row>
     <row r="172">
@@ -25477,17 +25557,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Net loss for the year – – –</t>
+          <t>Loss before other income (expense)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -25515,59 +25595,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J172" s="5" t="n">
+        <v>-0.101814</v>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>-0.120468</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>-0.120141</v>
+      </c>
+      <c r="M172" s="5" t="n">
+        <v>-0.059946</v>
+      </c>
+      <c r="N172" s="5" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="O172" s="5" t="n">
+        <v>-0.04743</v>
+      </c>
+      <c r="P172" s="5" t="n">
+        <v>-0.052452</v>
+      </c>
+      <c r="Q172" s="5" t="n">
+        <v>-0.051028</v>
+      </c>
+      <c r="R172" s="5" t="n">
+        <v>-0.055534</v>
       </c>
       <c r="S172" s="5" t="n">
-        <v>-0.040425</v>
+        <v>-0.055439</v>
       </c>
       <c r="T172" s="5" t="n">
-        <v>-0.040425</v>
+        <v>-0.052133</v>
       </c>
       <c r="U172" s="5" t="n">
-        <v>-0.040425</v>
+        <v>-0.052841</v>
       </c>
     </row>
     <row r="173">
@@ -25578,15 +25640,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 34,283,475 3,763,592 721,483</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Interest income (Note 4)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -25637,36 +25703,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O173" s="5" t="n">
+        <v>0.011935</v>
+      </c>
+      <c r="P173" s="5" t="n">
+        <v>0.011732</v>
+      </c>
+      <c r="Q173" s="5" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="R173" s="5" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="S173" s="5" t="n">
+        <v>0.011704</v>
       </c>
       <c r="T173" s="5" t="n">
-        <v>-0.175719</v>
+        <v>0.011732</v>
       </c>
       <c r="U173" s="5" t="n">
-        <v>-4.660794</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="174">
@@ -25677,12 +25733,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2025 34,283,475 3,763,592 721,483</t>
+          <t>Unrealized gain (loss) on marketable securities</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -25726,15 +25782,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M174" s="5" t="n">
+        <v>-0.000494</v>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>0.000798</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -25762,10 +25814,10 @@
         </is>
       </c>
       <c r="T174" s="5" t="n">
-        <v>-0.216645</v>
+        <v>-2.4e-05</v>
       </c>
       <c r="U174" s="5" t="n">
-        <v>-4.70172</v>
+        <v>0.000215</v>
       </c>
     </row>
     <row r="175">
@@ -25776,17 +25828,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
+          <t>Total other income (expense)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -25814,55 +25866,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J175" s="5" t="n">
+        <v>0.007706</v>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>0.056312</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>0.016574</v>
+      </c>
+      <c r="M175" s="5" t="n">
+        <v>-0.216145</v>
+      </c>
+      <c r="N175" s="5" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="O175" s="5" t="n">
+        <v>0.011137</v>
       </c>
       <c r="P175" s="5" t="n">
-        <v>0.0225</v>
+        <v>0.010934</v>
       </c>
       <c r="Q175" s="5" t="n">
-        <v>0.03</v>
+        <v>0.012299</v>
       </c>
       <c r="R175" s="5" t="n">
-        <v>0.03</v>
+        <v>0.0121</v>
       </c>
       <c r="S175" s="5" t="n">
-        <v>0.03</v>
+        <v>0.010187</v>
       </c>
       <c r="T175" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011708</v>
+      </c>
+      <c r="U175" s="5" t="n">
+        <v>0.011915</v>
       </c>
     </row>
     <row r="176">
@@ -25878,10 +25916,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -25922,42 +25964,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M176" s="5" t="n">
-        <v>-0.000494</v>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O176" s="5" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P176" s="5" t="n">
+        <v>-0.041518</v>
+      </c>
+      <c r="Q176" s="5" t="n">
+        <v>-0.038729</v>
+      </c>
+      <c r="R176" s="5" t="n">
+        <v>-0.043434</v>
       </c>
       <c r="S176" s="5" t="n">
-        <v>-0.001517</v>
+        <v>-0.045252</v>
       </c>
       <c r="T176" s="5" t="n">
-        <v>-2.4e-05</v>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.040425</v>
+      </c>
+      <c r="U176" s="5" t="n">
+        <v>-0.040926</v>
       </c>
     </row>
     <row r="177">
@@ -25968,15 +26006,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2022 34,283,475 3,763,592 721,483</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -26017,10 +26059,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M177" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -26047,11 +26087,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S177" s="5" t="n">
-        <v>-0.090042</v>
-      </c>
-      <c r="T177" s="5" t="n">
-        <v>-4.575117</v>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -26067,17 +26111,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Net loss for the year – –</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -26105,61 +26149,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="M178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="N178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="O178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="P178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="Q178" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="R178" s="5" t="n">
+        <v>34.283475</v>
       </c>
       <c r="S178" s="5" t="n">
-        <v>-0.045252</v>
+        <v>34.283475</v>
       </c>
       <c r="T178" s="5" t="n">
-        <v>-0.045252</v>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>34.283475</v>
+      </c>
+      <c r="U178" s="5" t="n">
+        <v>34.283475</v>
       </c>
     </row>
     <row r="179">
@@ -26175,7 +26199,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2023 32,283,475 3,763,592 721,483</t>
+          <t>Balance, March 31, 2023 34,283,475 3,763,592 721,483</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -26249,16 +26273,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S179" s="5" t="n">
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T179" s="5" t="n">
         <v>-0.135294</v>
       </c>
-      <c r="T179" s="5" t="n">
+      <c r="U179" s="5" t="n">
         <v>-4.620369</v>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="180">
@@ -26274,10 +26298,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 32,283,475 3,763,592 721,483</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Net loss for the year – – –</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -26349,15 +26377,13 @@
         </is>
       </c>
       <c r="S180" s="5" t="n">
-        <v>-0.175719</v>
+        <v>-0.040425</v>
       </c>
       <c r="T180" s="5" t="n">
-        <v>-4.660794</v>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.040425</v>
+      </c>
+      <c r="U180" s="5" t="n">
+        <v>-0.040425</v>
       </c>
     </row>
     <row r="181">
@@ -26368,12 +26394,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities (Note 5)</t>
+          <t>Balance, March 31, 2024 34,283,475 3,763,592 721,483</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -26442,21 +26468,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R181" s="5" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="S181" s="5" t="n">
-        <v>-0.001517</v>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T181" s="5" t="n">
+        <v>-0.175719</v>
+      </c>
+      <c r="U181" s="5" t="n">
+        <v>-4.660794</v>
       </c>
     </row>
     <row r="182">
@@ -26467,12 +26493,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>capital                                                                                                                                                                                                          notes</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>capital                                                                                                                                                                                                          notes total</t>
+          <t>Balance, March 31, 2025 34,283,475 3,763,592 721,483</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -26551,15 +26577,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T182" s="5" t="n">
+        <v>-0.216645</v>
+      </c>
+      <c r="U182" s="5" t="n">
+        <v>-4.70172</v>
       </c>
     </row>
     <row r="183">
@@ -26575,12 +26597,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Loss before other income</t>
+          <t>Management fees (Note 9)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -26593,17 +26615,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G183" s="5" t="n">
-        <v>-0.118102</v>
-      </c>
-      <c r="H183" s="5" t="n">
-        <v>-0.724948</v>
-      </c>
-      <c r="I183" s="5" t="n">
-        <v>-0.153098</v>
-      </c>
-      <c r="J183" s="5" t="n">
-        <v>-0.101814</v>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -26630,26 +26660,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P183" s="5" t="n">
+        <v>0.0225</v>
       </c>
       <c r="Q183" s="5" t="n">
-        <v>-0.051028</v>
+        <v>0.03</v>
       </c>
       <c r="R183" s="5" t="n">
-        <v>-0.055534</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03</v>
+      </c>
+      <c r="S183" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T183" s="5" t="n">
+        <v>0.03</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
@@ -26665,19 +26689,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Interest income (Note 4)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Unrealized loss on marketable securities</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -26718,41 +26738,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M184" s="5" t="n">
+        <v>-0.000494</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O184" s="5" t="n">
+        <v>-0.000798</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q184" s="5" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="R184" s="5" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S184" s="5" t="n">
+        <v>-0.001517</v>
+      </c>
+      <c r="T184" s="5" t="n">
+        <v>-2.4e-05</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -26768,12 +26784,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities (Note 5)</t>
+          <t>Balance, March 31, 2022 34,283,475 3,763,592 721,483</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -26837,21 +26853,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q185" s="5" t="n">
-        <v>0.000599</v>
-      </c>
-      <c r="R185" s="5" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S185" s="5" t="n">
+        <v>-0.090042</v>
+      </c>
+      <c r="T185" s="5" t="n">
+        <v>-4.575117</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
@@ -26867,17 +26883,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Total other income</t>
+          <t>Net loss for the year – –</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -26895,14 +26911,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H186" s="5" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="I186" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J186" s="5" t="n">
-        <v>0.007706</v>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -26934,21 +26956,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q186" s="5" t="n">
-        <v>0.012299</v>
-      </c>
-      <c r="R186" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S186" s="5" t="n">
+        <v>-0.045252</v>
+      </c>
+      <c r="T186" s="5" t="n">
+        <v>-0.045252</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -26964,19 +26986,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2023 32,283,475 3,763,592 721,483</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -27037,21 +27055,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q187" s="5" t="n">
-        <v>-0.038729</v>
-      </c>
-      <c r="R187" s="5" t="n">
-        <v>-0.043434</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S187" s="5" t="n">
+        <v>-0.135294</v>
+      </c>
+      <c r="T187" s="5" t="n">
+        <v>-4.620369</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -27067,19 +27085,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2024 32,283,475 3,763,592 721,483</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -27095,8 +27109,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -27148,15 +27164,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S188" s="5" t="n">
+        <v>-0.175719</v>
+      </c>
+      <c r="T188" s="5" t="n">
+        <v>-4.660794</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
@@ -27172,19 +27184,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Unrealized gain (loss) on marketable securities (Note 5)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -27195,17 +27203,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G189" s="5" t="n">
-        <v>31.812927</v>
-      </c>
-      <c r="H189" s="5" t="n">
-        <v>34.170872</v>
-      </c>
-      <c r="I189" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="J189" s="5" t="n">
-        <v>34.283475</v>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -27237,16 +27253,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q189" s="5" t="n">
-        <v>34.283475</v>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R189" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0004</v>
+      </c>
+      <c r="S189" s="5" t="n">
+        <v>-0.001517</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -27267,12 +27283,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>capital                                                                                                                                                                                                          notes</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Other income total</t>
+          <t>capital                                                                                                                                                                                                          notes total</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -27336,11 +27352,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q190" s="5" t="n">
-        <v>-0.090042</v>
-      </c>
-      <c r="R190" s="5" t="n">
-        <v>-0.043434</v>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -27366,15 +27386,19 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>capital                                                                                                                                                                                                      notes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>capital                                                                                                                                                                                                      notes total</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Loss before other income</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -27385,25 +27409,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G191" s="5" t="n">
+        <v>-0.118102</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>-0.724948</v>
+      </c>
+      <c r="I191" s="5" t="n">
+        <v>-0.153098</v>
+      </c>
+      <c r="J191" s="5" t="n">
+        <v>-0.101814</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -27435,15 +27451,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q191" s="5" t="n">
+        <v>-0.051028</v>
+      </c>
+      <c r="R191" s="5" t="n">
+        <v>-0.055534</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -27469,17 +27481,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Professional fees (Note 9)</t>
+          <t>Interest income (Note 4)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -27537,16 +27549,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P192" s="5" t="n">
-        <v>0.020157</v>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q192" s="5" t="n">
-        <v>0.013275</v>
-      </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0117</v>
+      </c>
+      <c r="R192" s="5" t="n">
+        <v>0.0117</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -27572,12 +27584,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities (Note 3)</t>
+          <t>Unrealized gain on marketable securities (Note 5)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -27606,11 +27618,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J193" s="5" t="n">
-        <v>0.020246</v>
-      </c>
-      <c r="K193" s="5" t="n">
-        <v>-0.020246</v>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -27632,16 +27648,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P193" s="5" t="n">
-        <v>-0.000798</v>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q193" s="5" t="n">
         <v>0.000599</v>
       </c>
-      <c r="R193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R193" s="5" t="n">
+        <v>0.0004</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -27667,17 +27683,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Management fees (Note 5)</t>
+          <t>Total other income</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -27690,32 +27706,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G194" s="5" t="n">
-        <v>0.032039</v>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H194" s="5" t="n">
-        <v>0.411655</v>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0345</v>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>0.007706</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L194" s="5" t="n">
-        <v>0.031652</v>
-      </c>
-      <c r="M194" s="5" t="n">
-        <v>0.008085</v>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -27727,18 +27745,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P194" s="5" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q194" s="5" t="n">
+        <v>0.012299</v>
+      </c>
+      <c r="R194" s="5" t="n">
+        <v>0.0121</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -27764,17 +27780,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Professional fees (Note 5)</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -27787,11 +27803,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G195" s="5" t="n">
-        <v>0.041295</v>
-      </c>
-      <c r="H195" s="5" t="n">
-        <v>0.197489</v>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -27808,30 +27828,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L195" s="5" t="n">
-        <v>0.042755</v>
-      </c>
-      <c r="M195" s="5" t="n">
-        <v>0.03875</v>
-      </c>
-      <c r="N195" s="5" t="n">
-        <v>0.036636</v>
-      </c>
-      <c r="O195" s="5" t="n">
-        <v>0.035727</v>
-      </c>
-      <c r="P195" s="5" t="n">
-        <v>0.020157</v>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q195" s="5" t="n">
+        <v>-0.038729</v>
+      </c>
+      <c r="R195" s="5" t="n">
+        <v>-0.043434</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -27857,15 +27883,19 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities (Note 3)</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -27881,10 +27911,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H196" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -27896,8 +27924,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K196" s="5" t="n">
-        <v>-0.020246</v>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -27914,11 +27944,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O196" s="5" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="P196" s="5" t="n">
-        <v>-0.000798</v>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -27954,17 +27988,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -27977,51 +28011,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G197" s="5" t="n">
+        <v>31.812927</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>34.170872</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>34.283475</v>
       </c>
       <c r="J197" s="5" t="n">
-        <v>-0.094108</v>
-      </c>
-      <c r="K197" s="5" t="n">
-        <v>-0.064156</v>
-      </c>
-      <c r="L197" s="5" t="n">
-        <v>-0.103567</v>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v>-0.276091</v>
-      </c>
-      <c r="N197" s="5" t="n">
-        <v>-0.0354</v>
-      </c>
-      <c r="O197" s="5" t="n">
-        <v>-0.036293</v>
-      </c>
-      <c r="P197" s="5" t="n">
-        <v>-0.041518</v>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>34.283475</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q197" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="R197" s="5" t="n">
+        <v>34.283475</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -28047,12 +28083,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>$ (36,293) (41,518) Deficit (4,415,447)</t>
+          <t>Other income total</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -28106,21 +28142,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O198" s="5" t="n">
-        <v>-4.492954</v>
-      </c>
-      <c r="P198" s="5" t="n">
-        <v>-4.451436</v>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q198" s="5" t="n">
+        <v>-0.090042</v>
+      </c>
+      <c r="R198" s="5" t="n">
+        <v>-0.043434</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -28146,12 +28182,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>capital                                                                                                                                                                                                      notes</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>– total</t>
+          <t>capital                                                                                                                                                                                                      notes total</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -28190,8 +28226,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L199" s="5" t="n">
-        <v>-0.000494</v>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -28247,15 +28285,19 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>$                                    other                                                         income                                                                  Accumulated                                                                                                            comprehensive                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      statements)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>$                                    other                                                         income                                                                  Accumulated                                                                                                            comprehensive                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      statements)</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Professional fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -28311,15 +28353,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P200" s="5" t="n">
+        <v>0.020157</v>
+      </c>
+      <c r="Q200" s="5" t="n">
+        <v>0.013275</v>
       </c>
       <c r="R200" t="inlineStr">
         <is>
@@ -28350,12 +28388,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>– –   –                                                  of</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>– –   –                                                  of part $ Amount 3,763,592 3,763,592</t>
+          <t>Unrealized gain (loss) on marketable securities (Note 3)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -28384,15 +28422,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J201" s="5" t="n">
+        <v>0.020246</v>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>-0.020246</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -28409,16 +28443,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O201" s="5" t="n">
-        <v>4e-06</v>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P201" s="5" t="n">
-        <v>3.763592</v>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000798</v>
+      </c>
+      <c r="Q201" s="5" t="n">
+        <v>0.000599</v>
       </c>
       <c r="R201" t="inlineStr">
         <is>
@@ -28449,15 +28483,19 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>an</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>Management fees (Note 5)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -28468,15 +28506,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G202" s="5" t="n">
+        <v>0.032039</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>0.411655</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -28493,15 +28527,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L202" s="5" t="n">
+        <v>0.031652</v>
+      </c>
+      <c r="M202" s="5" t="n">
+        <v>0.008085</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
@@ -28513,10 +28543,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P202" s="5" t="n">
+        <v>0.0225</v>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
@@ -28552,17 +28580,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Professional fees (Note 5)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -28575,43 +28603,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G203" s="5" t="n">
+        <v>0.041295</v>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>0.197489</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J203" s="5" t="n">
-        <v>0.007706</v>
-      </c>
-      <c r="K203" s="5" t="n">
-        <v>0.007974999999999999</v>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L203" s="5" t="n">
-        <v>0.016695</v>
+        <v>0.042755</v>
       </c>
       <c r="M203" s="5" t="n">
-        <v>0.036074</v>
+        <v>0.03875</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.036636</v>
       </c>
       <c r="O203" s="5" t="n">
-        <v>0.011935</v>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.035727</v>
+      </c>
+      <c r="P203" s="5" t="n">
+        <v>0.020157</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -28647,12 +28673,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Comprehensive income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities</t>
+          <t>Unrealized loss on marketable securities (Note 3)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -28686,10 +28712,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K204" s="5" t="n">
+        <v>-0.020246</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -28701,18 +28725,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N204" s="5" t="n">
-        <v>0.000798</v>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O204" s="5" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="P204" s="5" t="n">
+        <v>-0.000798</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -28748,12 +28770,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Comprehensive income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -28786,36 +28808,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J205" s="5" t="n">
+        <v>-0.094108</v>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>-0.064156</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>-0.103567</v>
+      </c>
+      <c r="M205" s="5" t="n">
+        <v>-0.276091</v>
       </c>
       <c r="N205" s="5" t="n">
-        <v>-0.034602</v>
+        <v>-0.0354</v>
       </c>
       <c r="O205" s="5" t="n">
         <v>-0.036293</v>
       </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P205" s="5" t="n">
+        <v>-0.041518</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -28851,19 +28863,15 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Comprehensive income</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>$ (36,293) (41,518) Deficit (4,415,447)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -28914,15 +28922,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O206" s="5" t="n">
+        <v>-4.492954</v>
+      </c>
+      <c r="P206" s="5" t="n">
+        <v>-4.451436</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -28958,19 +28962,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Comprehensive income</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>– total</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -29006,21 +29006,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L207" s="5" t="n">
+        <v>-0.000494</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N207" s="5" t="n">
-        <v>34.283475</v>
-      </c>
-      <c r="O207" s="5" t="n">
-        <v>34.283475</v>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
@@ -29061,12 +29063,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Comprehensive income</t>
+          <t>$                                    other                                                         income                                                                  Accumulated                                                                                                            comprehensive                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      statements)</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Comprehensive income total</t>
+          <t>$                                    other                                                         income                                                                  Accumulated                                                                                                            comprehensive                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      statements)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -29115,11 +29117,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N208" s="5" t="n">
-        <v>0.000304</v>
-      </c>
-      <c r="O208" s="5" t="n">
-        <v>0.000798</v>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
@@ -29160,12 +29166,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Comprehensive income</t>
+          <t>– –   –                                                  of</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$ (35,400) (36,293) Deficit (4,380,047)</t>
+          <t>– –   –                                                  of part $ Amount 3,763,592 3,763,592</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -29214,16 +29220,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N209" s="5" t="n">
-        <v>-4.451436</v>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O209" s="5" t="n">
-        <v>-4.415447</v>
-      </c>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4e-06</v>
+      </c>
+      <c r="P209" s="5" t="n">
+        <v>3.763592</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -29259,12 +29265,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Comprehensive income</t>
+          <t>an</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>(loss) (494) 798 – 304 (304)</t>
+          <t>an</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -29362,15 +29368,19 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>– –    – –                                                                                                                    these</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>– –    – –                                                                                                                    these of Amount 3,763,592 3,763,592</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -29396,31 +29406,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J211" s="5" t="n">
+        <v>0.007706</v>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>0.007974999999999999</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>0.016695</v>
+      </c>
+      <c r="M211" s="5" t="n">
+        <v>0.036074</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.0117</v>
       </c>
       <c r="O211" s="5" t="n">
-        <v>3.763592</v>
+        <v>0.011935</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
@@ -29461,12 +29463,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>part                                                       capital</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>part                                                       capital</t>
+          <t>Unrealized gain on marketable securities</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -29515,10 +29517,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N212" s="5" t="n">
+        <v>0.000798</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -29564,17 +29564,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -29617,18 +29617,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M213" s="5" t="n">
-        <v>-0.003453</v>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="5" t="n">
+        <v>-0.034602</v>
+      </c>
+      <c r="O213" s="5" t="n">
+        <v>-0.036293</v>
       </c>
       <c r="P213" t="inlineStr">
         <is>
@@ -29669,17 +29667,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Office and miscellaneous (Note 5)</t>
+          <t>Loss per share, basic and diluted</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -29717,14 +29715,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L214" s="5" t="n">
-        <v>0.026926</v>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v>0.016564</v>
-      </c>
-      <c r="N214" s="5" t="n">
-        <v>0.010464</v>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -29770,15 +29774,19 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Impairment of accrued interest receivable (Note 4)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -29819,18 +29827,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M215" s="5" t="n">
-        <v>-0.029119</v>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="5" t="n">
+        <v>34.283475</v>
+      </c>
+      <c r="O215" s="5" t="n">
+        <v>34.283475</v>
       </c>
       <c r="P215" t="inlineStr">
         <is>
@@ -29871,12 +29877,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Impairment of loans receivable (Note 4)</t>
+          <t>Comprehensive income total</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -29920,18 +29926,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M216" s="5" t="n">
-        <v>-0.2231</v>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="5" t="n">
+        <v>0.000304</v>
+      </c>
+      <c r="O216" s="5" t="n">
+        <v>0.000798</v>
       </c>
       <c r="P216" t="inlineStr">
         <is>
@@ -29972,19 +29976,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>$ (35,400) (36,293) Deficit (4,380,047)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -30010,25 +30010,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J217" s="5" t="n">
-        <v>-0.073862</v>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>-0.084402</v>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v>-0.103567</v>
-      </c>
-      <c r="M217" s="5" t="n">
-        <v>-0.276585</v>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N217" s="5" t="n">
-        <v>-0.034602</v>
-      </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.451436</v>
+      </c>
+      <c r="O217" s="5" t="n">
+        <v>-4.415447</v>
       </c>
       <c r="P217" t="inlineStr">
         <is>
@@ -30069,12 +30075,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Other income (expense) total</t>
+          <t>(loss) (494) 798 – 304 (304)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -30118,11 +30124,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M218" s="5" t="n">
-        <v>0.000798</v>
-      </c>
-      <c r="N218" s="5" t="n">
-        <v>-0.000494</v>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -30168,12 +30178,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>– –    – –                                                                                                                    these</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>$ (35,400) Deficit (4,103,956) (276,091)</t>
+          <t>– –    – –                                                                                                                    these of Amount 3,763,592 3,763,592</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -30217,16 +30227,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M219" s="5" t="n">
-        <v>-4.415447</v>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N219" s="5" t="n">
-        <v>-4.380047</v>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4e-06</v>
+      </c>
+      <c r="O219" s="5" t="n">
+        <v>3.763592</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -30267,12 +30277,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>part                                                       capital</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>(loss) – (494) – (494) 798</t>
+          <t>part                                                       capital</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -30316,8 +30326,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M220" s="5" t="n">
-        <v>0.000304</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
@@ -30368,15 +30380,19 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>– –   – –                                                                                                                            these</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>– –   – –                                                                                                                            these of Amount 3,763,592 3,763,592</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -30418,10 +30434,12 @@
         </is>
       </c>
       <c r="M221" s="5" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v>3.763592</v>
+        <v>-0.003453</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -30472,12 +30490,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Office and miscellaneous (Note 5)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -30516,15 +30534,13 @@
         </is>
       </c>
       <c r="L222" s="5" t="n">
-        <v>0.010008</v>
+        <v>0.026926</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>-0.003453</v>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016564</v>
+      </c>
+      <c r="N222" s="5" t="n">
+        <v>0.010464</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -30570,19 +30586,15 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Impairment of accrued interest receivable (Note 4)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -30593,26 +30605,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G223" s="5" t="n">
-        <v>0.012222</v>
-      </c>
-      <c r="H223" s="5" t="n">
-        <v>0.016021</v>
-      </c>
-      <c r="I223" s="5" t="n">
-        <v>0.012685</v>
-      </c>
-      <c r="J223" s="5" t="n">
-        <v>0.010857</v>
-      </c>
-      <c r="K223" s="5" t="n">
-        <v>0.016012</v>
-      </c>
-      <c r="L223" s="5" t="n">
-        <v>0.008800000000000001</v>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M223" s="5" t="n">
-        <v>0.01025</v>
+        <v>-0.029119</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -30668,7 +30692,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of marketable securities</t>
+          <t>Impairment of loans receivable (Note 4)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -30707,13 +30731,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L224" s="5" t="n">
-        <v>-0.000121</v>
-      </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M224" s="5" t="n">
+        <v>-0.2231</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
@@ -30769,10 +30793,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Impairment of accrued interest receivable(Note 4)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>Comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -30798,28 +30826,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J225" s="5" t="n">
+        <v>-0.073862</v>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>-0.084402</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>-0.103567</v>
       </c>
       <c r="M225" s="5" t="n">
-        <v>-0.029119</v>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.276585</v>
+      </c>
+      <c r="N225" s="5" t="n">
+        <v>-0.034602</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -30865,12 +30885,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>$ Deficit (4,000,389) (103,567) (4,103,956)</t>
+          <t>Other income (expense) total</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -30909,16 +30929,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L226" s="5" t="n">
-        <v>-4.380047</v>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M226" s="5" t="n">
-        <v>-0.276091</v>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000798</v>
+      </c>
+      <c r="N226" s="5" t="n">
+        <v>-0.000494</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -30964,12 +30984,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>–  – –                                                                                                                                      these</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>–  – –                                                                                                                                      these of Amount 3,763,592 3,763,592</t>
+          <t>$ (35,400) Deficit (4,103,956) (276,091)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -31008,16 +31028,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L227" s="5" t="n">
-        <v>4e-06</v>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M227" s="5" t="n">
-        <v>3.763592</v>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.415447</v>
+      </c>
+      <c r="N227" s="5" t="n">
+        <v>-4.380047</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -31063,19 +31083,15 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>(loss) – (494) – (494) 798</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -31086,30 +31102,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G228" s="5" t="n">
-        <v>4.4e-05</v>
-      </c>
-      <c r="H228" s="5" t="n">
-        <v>3.6e-05</v>
-      </c>
-      <c r="I228" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="J228" s="5" t="n">
-        <v>2.4e-05</v>
-      </c>
-      <c r="K228" s="5" t="n">
-        <v>9.000000000000001e-05</v>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M228" s="5" t="n">
+        <v>0.000304</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -31160,19 +31184,15 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>– –   – –                                                                                                                            these</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>– –   – –                                                                                                                            these of Amount 3,763,592 3,763,592</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -31208,18 +31228,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L229" s="5" t="n">
-        <v>0.010008</v>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" s="5" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="N229" s="5" t="n">
+        <v>3.763592</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -31270,12 +31288,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Management fees (Note 6)</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -31293,27 +31311,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H230" s="5" t="n">
-        <v>0.411655</v>
-      </c>
-      <c r="I230" s="5" t="n">
-        <v>0.032059</v>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K230" s="5" t="n">
-        <v>0.032101</v>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L230" s="5" t="n">
-        <v>0.031652</v>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010008</v>
+      </c>
+      <c r="M230" s="5" t="n">
+        <v>-0.003453</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -31369,7 +31391,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Office and miscellaneous (Note 6)</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -31382,41 +31404,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F231" s="5" t="n">
+        <v>0.005719</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>0.012222</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>0.016021</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>0.012685</v>
+      </c>
+      <c r="J231" s="5" t="n">
+        <v>0.010857</v>
       </c>
       <c r="K231" s="5" t="n">
-        <v>0.027962</v>
+        <v>0.016012</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>0.026926</v>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="M231" s="5" t="n">
+        <v>0.01025</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -31467,19 +31477,15 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Professional fees (Note 6)</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Gain (loss) on sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -31495,22 +31501,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H232" s="5" t="n">
-        <v>0.197489</v>
-      </c>
-      <c r="I232" s="5" t="n">
-        <v>0.044112</v>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K232" s="5" t="n">
-        <v>0.044303</v>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L232" s="5" t="n">
-        <v>0.042755</v>
+        <v>-0.000121</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
@@ -31571,7 +31583,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of marketable securities (Note 3)</t>
+          <t>Impairment of accrued interest receivable(Note 4)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -31605,16 +31617,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K233" s="5" t="n">
-        <v>0.017801</v>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v>-0.000121</v>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" s="5" t="n">
+        <v>-0.029119</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -31665,12 +31679,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Provision for loan receivable (Note 4)</t>
+          <t>$ Deficit (4,000,389) (103,567) (4,103,956)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -31704,18 +31718,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K234" s="5" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>-4.380047</v>
+      </c>
+      <c r="M234" s="5" t="n">
+        <v>-0.276091</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -31766,12 +31778,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>–  – –                                                                                                                                      these</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Write-off of accounts payable</t>
+          <t>–  – –                                                                                                                                      these of Amount 3,763,592 3,763,592</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -31805,18 +31817,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K235" s="5" t="n">
-        <v>0.055536</v>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>3.763592</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -31867,50 +31877,46 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>$ (64,156) Deficit (3,936,233) (4,000,389)</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F236" s="5" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>4.4e-05</v>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>3.6e-05</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>2.8e-05</v>
+      </c>
+      <c r="J236" s="5" t="n">
+        <v>2.4e-05</v>
       </c>
       <c r="K236" s="5" t="n">
-        <v>-4.103956</v>
-      </c>
-      <c r="L236" s="5" t="n">
-        <v>-0.103567</v>
+        <v>9.000000000000001e-05</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -31966,15 +31972,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>– –  –                                                                                                                                        these</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>– –  –                                                                                                                                        these of Amount 3,763,592 3,763,592</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -32005,11 +32015,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K237" s="5" t="n">
-        <v>4e-06</v>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L237" s="5" t="n">
-        <v>3.763592</v>
+        <v>0.010008</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -32063,15 +32075,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Management fees (Note 6)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -32089,30 +32105,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H238" s="5" t="n">
+        <v>0.411655</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>0.032059</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K238" s="5" t="n">
+        <v>0.032101</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>0.031652</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -32173,7 +32181,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Management fees (Note 7)</t>
+          <t>Office and miscellaneous (Note 6)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -32206,16 +32214,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J239" s="5" t="n">
-        <v>0.032101</v>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>0.032101</v>
-      </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027962</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>0.026926</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
@@ -32276,12 +32284,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Office and miscellaneous (Note 7)</t>
+          <t>Professional fees (Note 6)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -32299,26 +32307,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J240" s="5" t="n">
-        <v>0.021082</v>
+      <c r="H240" s="5" t="n">
+        <v>0.197489</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>0.044112</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K240" s="5" t="n">
-        <v>0.027962</v>
-      </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.044303</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>0.042755</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
@@ -32374,19 +32378,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Gain (loss) on sale of marketable securities (Note 3)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -32412,16 +32412,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J241" s="5" t="n">
-        <v>0.03775</v>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>0.044303</v>
-      </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017801</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>-0.000121</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Gain on sale of marketable securities (Note 3)</t>
+          <t>Provision for loan receivable (Note 4)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -32517,7 +32517,7 @@
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>0.017801</v>
+        <v>-0.025</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>$ (94,108) (64,156) Deficit (3,842,125)</t>
+          <t>Write-off of accounts payable</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -32612,11 +32612,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J243" s="5" t="n">
-        <v>-4.000389</v>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K243" s="5" t="n">
-        <v>-3.936233</v>
+        <v>0.055536</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -32677,12 +32679,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>– –  – –                                                                                                                                these</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>– –  – –                                                                                                                                these of Amount 3,763,592 3,763,592</t>
+          <t>$ (64,156) Deficit (3,936,233) (4,000,389)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -32711,16 +32713,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J244" s="5" t="n">
-        <v>4e-06</v>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K244" s="5" t="n">
-        <v>3.763592</v>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.103956</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>-0.103567</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
@@ -32776,12 +32778,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>– –  –                                                                                                                                        these</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 6)</t>
+          <t>– –  –                                                                                                                                        these of Amount 3,763,592 3,763,592</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -32805,23 +32807,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I245" s="5" t="n">
-        <v>0.025</v>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K245" s="5" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>3.763592</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -32875,19 +32875,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Office and miscellaneous (Note 8)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -32910,11 +32906,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I246" s="5" t="n">
-        <v>0.039214</v>
-      </c>
-      <c r="J246" s="5" t="n">
-        <v>0.021082</v>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -32985,12 +32985,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Professional fees (Note 8)</t>
+          <t>Management fees (Note 7)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -33013,16 +33013,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I247" s="5" t="n">
-        <v>0.044112</v>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J247" s="5" t="n">
-        <v>0.03775</v>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032101</v>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>0.032101</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -33083,15 +33083,19 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Gain on disposal of exploration and evaluation asset (Note 6)</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>Office and miscellaneous (Note 7)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -33112,18 +33116,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I248" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" s="5" t="n">
+        <v>0.021082</v>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>0.027962</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -33184,17 +33186,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Professional fees (Note 7)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -33223,12 +33225,10 @@
         </is>
       </c>
       <c r="J249" s="5" t="n">
-        <v>0.007706</v>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03775</v>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>0.044303</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -33289,19 +33289,15 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on sale of marketable securities (Note 3)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -33322,16 +33318,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I250" s="5" t="n">
-        <v>-0.148098</v>
-      </c>
-      <c r="J250" s="5" t="n">
-        <v>-0.094108</v>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>0.017801</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -33392,12 +33390,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities (Note 3)</t>
+          <t>$ (94,108) (64,156) Deficit (3,842,125)</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -33427,12 +33425,10 @@
         </is>
       </c>
       <c r="J251" s="5" t="n">
-        <v>0.020246</v>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.000389</v>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>-3.936233</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -33493,19 +33489,15 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>– –  – –                                                                                                                                these</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>– –  – –                                                                                                                                these of Amount 3,763,592 3,763,592</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -33526,16 +33518,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I252" s="5" t="n">
-        <v>-0.148098</v>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J252" s="5" t="n">
-        <v>-0.073862</v>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4e-06</v>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>3.763592</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -33596,12 +33588,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>$ (94,108) Deficit (3,694,027) (148,098)</t>
+          <t>Impairment of exploration and evaluation assets (Note 6)</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -33626,10 +33618,12 @@
         </is>
       </c>
       <c r="I253" s="5" t="n">
-        <v>-3.936233</v>
-      </c>
-      <c r="J253" s="5" t="n">
-        <v>-3.842125</v>
+        <v>0.025</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -33695,15 +33689,19 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>–  – –                                                                                                                                   these</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>–  – –                                                                                                                                   these of Amount 3,763,592 3,763,592</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>Office and miscellaneous (Note 8)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -33725,10 +33723,10 @@
         </is>
       </c>
       <c r="I254" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.039214</v>
       </c>
       <c r="J254" s="5" t="n">
-        <v>3.763592</v>
+        <v>0.021082</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -33799,12 +33797,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Professional fees (Note 8)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -33817,21 +33815,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G255" s="5" t="n">
-        <v>0.003883</v>
-      </c>
-      <c r="H255" s="5" t="n">
-        <v>0.075919</v>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>0.044112</v>
+      </c>
+      <c r="J255" s="5" t="n">
+        <v>0.03775</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -33897,12 +33895,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 4)</t>
+          <t>Gain on disposal of exploration and evaluation asset (Note 6)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -33927,7 +33925,7 @@
         </is>
       </c>
       <c r="I256" s="5" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -34003,10 +34001,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Flow-through share premium</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -34022,18 +34024,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H257" s="5" t="n">
-        <v>0.0345</v>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J257" s="5" t="n">
+        <v>0.007706</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
@@ -34104,10 +34106,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Gain on disposal of exploration and evaluation asset (Note 4)</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -34129,12 +34135,10 @@
         </is>
       </c>
       <c r="I258" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.148098</v>
+      </c>
+      <c r="J258" s="5" t="n">
+        <v>-0.094108</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
@@ -34205,14 +34209,10 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for year</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized gain on marketable securities (Note 3)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -34223,19 +34223,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G259" s="5" t="n">
-        <v>-0.118102</v>
-      </c>
-      <c r="H259" s="5" t="n">
-        <v>-0.690448</v>
-      </c>
-      <c r="I259" s="5" t="n">
-        <v>-0.148098</v>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" s="5" t="n">
+        <v>0.020246</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -34301,15 +34305,19 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Recovery of GST previously written off</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>Comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -34320,23 +34328,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G260" s="5" t="n">
-        <v>-0.010567</v>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I260" s="5" t="n">
+        <v>-0.148098</v>
+      </c>
+      <c r="J260" s="5" t="n">
+        <v>-0.073862</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -34402,19 +34408,15 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>$ (94,108) Deficit (3,694,027) (148,098)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -34425,23 +34427,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G261" s="5" t="n">
-        <v>0.024</v>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I261" s="5" t="n">
+        <v>-3.936233</v>
+      </c>
+      <c r="J261" s="5" t="n">
+        <v>-3.842125</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -34507,24 +34507,24 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>–  – –                                                                                                                                   these</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Amortization $</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E262" s="5" t="n">
-        <v>6.8e-05</v>
-      </c>
-      <c r="F262" s="5" t="n">
-        <v>0.00389</v>
+          <t>–  – –                                                                                                                                   these of Amount 3,763,592 3,763,592</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -34536,15 +34536,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I262" s="5" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="J262" s="5" t="n">
+        <v>3.763592</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -34610,36 +34606,34 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E263" s="5" t="n">
-        <v>0.0052</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G263" s="5" t="n">
+        <v>0.003883</v>
+      </c>
+      <c r="H263" s="5" t="n">
+        <v>0.075919</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -34715,24 +34709,24 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E264" s="5" t="n">
-        <v>0.006766</v>
-      </c>
-      <c r="F264" s="5" t="n">
-        <v>0.002783</v>
+          <t>Impairment of exploration and evaluation assets (Note 4)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -34744,10 +34738,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I264" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -34818,34 +34810,32 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E265" s="5" t="n">
-        <v>0.000293</v>
-      </c>
-      <c r="F265" s="5" t="n">
-        <v>9.7e-05</v>
+          <t>Flow-through share premium</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H265" s="5" t="n">
+        <v>0.0345</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -34921,24 +34911,24 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Management fees – Note 5</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E266" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F266" s="5" t="n">
-        <v>0.03</v>
+          <t>Gain on disposal of exploration and evaluation asset (Note 4)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -34950,10 +34940,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I266" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -35024,35 +35012,37 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Office expenses</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" s="5" t="n">
-        <v>0.007774</v>
-      </c>
-      <c r="F267" s="5" t="n">
-        <v>0.008423999999999999</v>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for year</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="n">
+        <v>-0.118102</v>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>-0.690448</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>-0.148098</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -35123,29 +35113,27 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Professional fees – Note 5</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E268" s="5" t="n">
-        <v>0.049181</v>
-      </c>
-      <c r="F268" s="5" t="n">
-        <v>0.043193</v>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Recovery of GST previously written off</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="n">
+        <v>-0.010567</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -35226,7 +35214,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -35239,16 +35227,16 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E269" s="5" t="n">
-        <v>0.0252</v>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F269" s="5" t="n">
         <v>0.0252</v>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G269" s="5" t="n">
+        <v>0.024</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -35329,12 +35317,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
+          <t>Management fees (Note 4)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35342,16 +35330,16 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E270" s="5" t="n">
-        <v>0.0045</v>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F270" s="5" t="n">
-        <v>0.002936</v>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03</v>
+      </c>
+      <c r="G270" s="5" t="n">
+        <v>0.032039</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -35432,29 +35420,29 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Professional fees (Note 4)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E271" s="5" t="n">
-        <v>-0.128982</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F271" s="5" t="n">
-        <v>-0.116523</v>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.043193</v>
+      </c>
+      <c r="G271" s="5" t="n">
+        <v>0.041295</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -35535,25 +35523,29 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" s="5" t="n">
-        <v>-2.639972</v>
+          <t>Net loss and comprehensive loss for year</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F272" s="5" t="n">
-        <v>-2.768954</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.116523</v>
+      </c>
+      <c r="G272" s="5" t="n">
+        <v>-0.118102</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -35634,25 +35626,25 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Deficit, end of year $</t>
+          <t>Deficit, beginning of year</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" s="5" t="n">
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="n">
         <v>-2.768954</v>
       </c>
-      <c r="F273" s="5" t="n">
+      <c r="G273" s="5" t="n">
         <v>-2.885477</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -35733,29 +35725,25 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E274" s="5" t="n">
-        <v>-1e-08</v>
+          <t>Deficit, end of year</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F274" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.885477</v>
+      </c>
+      <c r="G274" s="5" t="n">
+        <v>-3.003579</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -35836,96 +35824,1637 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="n">
+        <v>19.87868</v>
+      </c>
+      <c r="G276" s="5" t="n">
+        <v>31.812927</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
           <t>Administrative expenses</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Amortization $</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>6.8e-05</v>
+      </c>
+      <c r="F277" s="5" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>0.006766</v>
+      </c>
+      <c r="F279" s="5" t="n">
+        <v>0.002783</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>0.000293</v>
+      </c>
+      <c r="F280" s="5" t="n">
+        <v>9.7e-05</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Management fees – Note 5</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F281" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Office expenses</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="n">
+        <v>0.007774</v>
+      </c>
+      <c r="F282" s="5" t="n">
+        <v>0.008423999999999999</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Professional fees – Note 5</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="n">
+        <v>0.049181</v>
+      </c>
+      <c r="F283" s="5" t="n">
+        <v>0.043193</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="F284" s="5" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="F285" s="5" t="n">
+        <v>0.002936</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="n">
+        <v>-0.128982</v>
+      </c>
+      <c r="F286" s="5" t="n">
+        <v>-0.116523</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" s="5" t="n">
+        <v>-2.639972</v>
+      </c>
+      <c r="F287" s="5" t="n">
+        <v>-2.768954</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Deficit, end of year $</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" s="5" t="n">
+        <v>-2.768954</v>
+      </c>
+      <c r="F288" s="5" t="n">
+        <v>-2.885477</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F289" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
         <is>
           <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D290" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E275" s="5" t="n">
+      <c r="E290" s="5" t="n">
         <v>12.133475</v>
       </c>
-      <c r="F275" s="5" t="n">
+      <c r="F290" s="5" t="n">
         <v>19.87868</v>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U275" t="inlineStr">
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
